--- a/questionnaire_templates/021_symbiotic_relationships_quiz--questionnaire_templates.xlsx
+++ b/questionnaire_templates/021_symbiotic_relationships_quiz--questionnaire_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1106,8 +1106,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1135,12 +1135,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1152,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1203,12 +1203,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1220,12 +1220,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1237,12 +1237,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1254,12 +1254,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1271,12 +1271,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1305,12 +1305,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1322,12 +1322,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1339,12 +1339,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1356,12 +1356,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1373,12 +1373,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1407,12 +1407,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1441,12 +1441,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1458,12 +1458,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1475,12 +1475,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1492,12 +1492,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1509,12 +1509,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1543,12 +1543,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1560,12 +1560,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1577,12 +1577,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1594,12 +1594,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1611,12 +1611,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1628,12 +1628,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1662,12 +1662,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1679,12 +1679,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1696,12 +1696,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1713,12 +1713,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1730,12 +1730,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1747,12 +1747,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1764,12 +1764,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1781,12 +1781,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1798,12 +1798,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1815,12 +1815,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1832,12 +1832,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1849,12 +1849,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1883,12 +1883,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1900,12 +1900,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1917,12 +1917,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1934,12 +1934,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1951,12 +1951,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1968,12 +1968,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1985,12 +1985,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -2002,12 +2002,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -2019,12 +2019,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -2036,12 +2036,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -2053,12 +2053,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -2087,12 +2087,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -2121,12 +2121,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -2138,12 +2138,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -2155,12 +2155,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -2172,12 +2172,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -2189,12 +2189,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -2206,12 +2206,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -2223,12 +2223,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -2240,12 +2240,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -2257,12 +2257,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -2274,12 +2274,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -2291,12 +2291,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
